--- a/data/gravel/Basso Palta 2025.xlsx
+++ b/data/gravel/Basso Palta 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0FBA0D-576C-5949-A5F4-8A9441FE0453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D6549A-EEF7-5F4C-82D1-E62BD120346C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="1480" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -260,9 +260,6 @@
     <t>rider_max_spec</t>
   </si>
   <si>
-    <t>both</t>
-  </si>
-  <si>
     <t>XS</t>
   </si>
   <si>
@@ -342,6 +339,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>drop bar</t>
   </si>
 </sst>
 </file>
@@ -722,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -730,7 +730,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -754,7 +754,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -773,7 +773,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -791,19 +791,19 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -811,7 +811,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="7">
         <v>410</v>
@@ -834,7 +834,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="7">
         <v>495</v>
@@ -857,7 +857,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="7">
         <v>354</v>
@@ -880,7 +880,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" s="7">
         <v>528</v>
@@ -903,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" s="7">
         <v>75</v>
@@ -926,7 +926,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" s="7">
         <v>68</v>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" s="7">
         <v>425</v>
@@ -969,10 +969,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16" s="7">
         <v>591</v>
@@ -992,10 +992,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" s="7">
         <v>285</v>
@@ -1018,7 +1018,7 @@
         <v>9</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18" s="7">
         <v>110</v>
@@ -1046,7 +1046,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C19" s="7">
         <v>1006</v>
@@ -1069,7 +1069,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C20" s="1">
         <v>71</v>
@@ -1092,7 +1092,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C21" s="1">
         <v>420</v>
@@ -1115,7 +1115,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C22" s="1">
         <v>80</v>
@@ -1152,7 +1152,7 @@
         <v>162</v>
       </c>
       <c r="I25" s="8">
-        <f t="shared" ref="I25:I31" si="1">0.42*H25</f>
+        <f t="shared" ref="I25:I28" si="1">0.42*H25</f>
         <v>68.039999999999992</v>
       </c>
       <c r="K25" s="1">
@@ -1204,7 +1204,7 @@
         <v>69.3</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
@@ -1308,7 +1308,7 @@
         <v>76.05</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -1324,7 +1324,7 @@
         <v>76.5</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
@@ -1355,19 +1355,19 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C36" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="E36" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="F36" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="G36" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="3"/>
@@ -1419,7 +1419,7 @@
         <v>80.5</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
@@ -1427,7 +1427,7 @@
         <v>68</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="3"/>
@@ -1459,7 +1459,7 @@
         <v>31</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H41" s="4">
         <f t="shared" si="3"/>
@@ -1552,7 +1552,7 @@
         <v>84.64</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
@@ -1777,7 +1777,7 @@
         <v>65</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Basso Palta 2025.xlsx
+++ b/data/gravel/Basso Palta 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D6549A-EEF7-5F4C-82D1-E62BD120346C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E48E56-FEFF-C544-94AB-402398CBB6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29940" yWindow="-18720" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -342,6 +342,9 @@
   </si>
   <si>
     <t>drop bar</t>
+  </si>
+  <si>
+    <t>https://cdn.s2api.it/prod/2023/09/Palta_Mullet_Sonic_White-Poseidon.webp</t>
   </si>
 </sst>
 </file>
@@ -758,6 +761,9 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>

--- a/data/gravel/Basso Palta 2025.xlsx
+++ b/data/gravel/Basso Palta 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E48E56-FEFF-C544-94AB-402398CBB6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25C34DC-6864-E140-8B1C-BFBC22C8B806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29940" yWindow="-18720" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,12 @@
   </si>
   <si>
     <t>https://cdn.s2api.it/prod/2023/09/Palta_Mullet_Sonic_White-Poseidon.webp</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>San Zenone degli Ezzelini, Province of Treviso, Italy</t>
   </si>
 </sst>
 </file>
@@ -713,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1786,6 +1792,14 @@
         <v>101</v>
       </c>
     </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Basso Palta 2025.xlsx
+++ b/data/gravel/Basso Palta 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25C34DC-6864-E140-8B1C-BFBC22C8B806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA39DA96-A634-F143-A41B-BE1A94328401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29940" yWindow="-18720" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,24 @@
   </si>
   <si>
     <t>San Zenone degli Ezzelini, Province of Treviso, Italy</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -719,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1446,7 +1464,7 @@
         <v>176</v>
       </c>
       <c r="I39" s="8">
-        <f t="shared" ref="I39:I55" si="4">0.46*H39</f>
+        <f t="shared" ref="I39:I61" si="4">0.46*H39</f>
         <v>80.960000000000008</v>
       </c>
     </row>
@@ -1543,7 +1561,7 @@
         <v>36</v>
       </c>
       <c r="H46" s="4">
-        <f t="shared" ref="H46:H55" si="5">H45+1</f>
+        <f t="shared" ref="H46:H61" si="5">H45+1</f>
         <v>183</v>
       </c>
       <c r="I46" s="8">
@@ -1627,176 +1645,218 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H52" s="4"/>
+      <c r="I52" s="8"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H53" s="4"/>
+      <c r="I53" s="8"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H54" s="4"/>
+      <c r="I54" s="8"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="8"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H56" s="4"/>
+      <c r="I56" s="8"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="8"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H52" s="4">
-        <f t="shared" si="5"/>
+      <c r="H58" s="4">
+        <f>H51+1</f>
         <v>189</v>
       </c>
-      <c r="I52" s="8">
+      <c r="I58" s="8">
         <f t="shared" si="4"/>
         <v>86.94</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H53" s="4">
+      <c r="H59" s="4">
         <f t="shared" si="5"/>
         <v>190</v>
       </c>
-      <c r="I53" s="8">
+      <c r="I59" s="8">
         <f t="shared" si="4"/>
         <v>87.4</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="1" t="s">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H54" s="4">
+      <c r="H60" s="4">
         <f t="shared" si="5"/>
         <v>191</v>
       </c>
-      <c r="I54" s="8">
+      <c r="I60" s="8">
         <f t="shared" si="4"/>
         <v>87.86</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H55" s="4">
+      <c r="H61" s="4">
         <f t="shared" si="5"/>
         <v>192</v>
       </c>
-      <c r="I55" s="8">
+      <c r="I61" s="8">
         <f t="shared" si="4"/>
         <v>88.320000000000007</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="1">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B71" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73" s="1">
-        <v>4975</v>
+        <v>57</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B79" s="1">
+        <v>4975</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>105</v>
       </c>
     </row>
